--- a/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Collegetown_2025-10-10.xlsx
+++ b/WorkBot/refactor/data/orders/Webstaurant/Webstaurant_Collegetown_2025-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,39 +446,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>544SYPFR061F</t>
+          <t>263Tabs</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Monin - Lavender</t>
+          <t>Sanitizer Tablets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>35.99</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>263Tabs</t>
+          <t>147LCDETLSPK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sanitizer Tablets</t>
+          <t>Bar Glass Cleaner</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -488,37 +488,10 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
-        <is>
-          <t>35.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>147LCDETLSPK</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bar Glass Cleaner</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>30.99</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>30.99</t>
         </is>
